--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="按日合计" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="参数" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -794,19 +795,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>672.249</v>
+        <v>614.933</v>
       </c>
       <c r="E11" t="n">
-        <v>7499.95</v>
+        <v>6861.985</v>
       </c>
       <c r="F11" t="n">
-        <v>20249.866</v>
+        <v>18527.359</v>
       </c>
       <c r="G11" t="n">
         <v>2.101</v>
       </c>
       <c r="H11" t="n">
-        <v>425.532</v>
+        <v>389.336</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -829,19 +830,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>218.016</v>
+        <v>212.457</v>
       </c>
       <c r="E12" t="n">
-        <v>2398.18</v>
+        <v>2337.028</v>
       </c>
       <c r="F12" t="n">
-        <v>6475.085</v>
+        <v>6309.976</v>
       </c>
       <c r="G12" t="n">
         <v>1.099</v>
       </c>
       <c r="H12" t="n">
-        <v>71.154</v>
+        <v>69.34</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -864,19 +865,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>85.45099999999999</v>
+        <v>78.309</v>
       </c>
       <c r="E13" t="n">
-        <v>939.965</v>
+        <v>861.396</v>
       </c>
       <c r="F13" t="n">
-        <v>2537.906</v>
+        <v>2325.768</v>
       </c>
       <c r="G13" t="n">
         <v>1.143</v>
       </c>
       <c r="H13" t="n">
-        <v>29.017</v>
+        <v>26.591</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -899,23 +900,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.08</v>
+        <v>83.342</v>
       </c>
       <c r="E14" t="n">
-        <v>780.799</v>
+        <v>916.763</v>
       </c>
       <c r="F14" t="n">
-        <v>2108.157</v>
+        <v>2475.259</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>1.545</v>
       </c>
       <c r="H14" t="n">
-        <v>45.958</v>
+        <v>38.243</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P3、P2、P1</t>
+          <t>P30、P28</t>
         </is>
       </c>
     </row>
@@ -934,23 +935,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>52.813</v>
+        <v>89.502</v>
       </c>
       <c r="E15" t="n">
-        <v>580.944</v>
+        <v>895.016</v>
       </c>
       <c r="F15" t="n">
-        <v>1568.548</v>
+        <v>2416.545</v>
       </c>
       <c r="G15" t="n">
-        <v>1.545</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
-        <v>24.234</v>
+        <v>52.681</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P30、P28</t>
+          <t>P3、P2、P1</t>
         </is>
       </c>
     </row>
@@ -969,19 +970,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72.69199999999999</v>
+        <v>78.67100000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>726.919</v>
+        <v>786.705</v>
       </c>
       <c r="F16" t="n">
-        <v>1962.682</v>
+        <v>2124.105</v>
       </c>
       <c r="G16" t="n">
         <v>1.375</v>
       </c>
       <c r="H16" t="n">
-        <v>26.987</v>
+        <v>29.206</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1004,19 +1005,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>662.211</v>
+        <v>685.884</v>
       </c>
       <c r="E17" t="n">
-        <v>7209.631</v>
+        <v>7469.899</v>
       </c>
       <c r="F17" t="n">
-        <v>19466.004</v>
+        <v>20168.728</v>
       </c>
       <c r="G17" t="n">
         <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>159.688</v>
+        <v>165.453</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1232,13 +1233,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>10838.095</v>
+        <v>10060.408</v>
       </c>
       <c r="E4" t="n">
-        <v>29262.857</v>
+        <v>27163.103</v>
       </c>
       <c r="F4" t="n">
-        <v>525.703</v>
+        <v>485.266</v>
       </c>
     </row>
     <row r="5">
@@ -1254,13 +1255,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>9298.293</v>
+        <v>10068.384</v>
       </c>
       <c r="E5" t="n">
-        <v>25105.391</v>
+        <v>27184.637</v>
       </c>
       <c r="F5" t="n">
-        <v>256.867</v>
+        <v>285.583</v>
       </c>
     </row>
     <row r="6">
@@ -1283,6 +1284,172 @@
       </c>
       <c r="F6" t="n">
         <v>99.717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>外推(m)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连接半径(m)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>最小块段(m²)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>接综合图(m)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>矿界自检</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4 个矿孔原本落在矿界外（P14、P17、P18、P19）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0922</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2 个矿孔原本落在矿界外（BL1、BL6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2 个矿孔原本落在矿界外（P1、P31）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>117.877</v>
+        <v>214.332</v>
       </c>
       <c r="E8" t="n">
-        <v>502.263</v>
+        <v>948.674</v>
       </c>
       <c r="F8" t="n">
-        <v>1356.111</v>
+        <v>2561.42</v>
       </c>
       <c r="G8" t="n">
         <v>1.727</v>
       </c>
       <c r="H8" t="n">
-        <v>23.416</v>
+        <v>44.227</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>202.678</v>
+        <v>308.969</v>
       </c>
       <c r="E9" t="n">
-        <v>714.737</v>
+        <v>1090.677</v>
       </c>
       <c r="F9" t="n">
-        <v>1929.789</v>
+        <v>2944.827</v>
       </c>
       <c r="G9" t="n">
         <v>1.333</v>
       </c>
       <c r="H9" t="n">
-        <v>25.721</v>
+        <v>39.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -760,58 +760,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>123.334</v>
+        <v>253.006</v>
       </c>
       <c r="E10" t="n">
-        <v>269.444</v>
+        <v>2728.153</v>
       </c>
       <c r="F10" t="n">
-        <v>727.498</v>
+        <v>7366.014</v>
       </c>
       <c r="G10" t="n">
-        <v>0.695</v>
+        <v>0.824</v>
       </c>
       <c r="H10" t="n">
-        <v>5.056</v>
+        <v>60.675</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BL4、BL3</t>
+          <t>P16、P15、P9、P17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>0922</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.500-3.000</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>614.933</v>
+        <v>283.238</v>
       </c>
       <c r="E11" t="n">
-        <v>6861.985</v>
+        <v>561.562</v>
       </c>
       <c r="F11" t="n">
-        <v>18527.359</v>
+        <v>1516.216</v>
       </c>
       <c r="G11" t="n">
-        <v>2.101</v>
+        <v>0.695</v>
       </c>
       <c r="H11" t="n">
-        <v>389.336</v>
+        <v>10.538</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>P38、P36、P33、P12、P30、P34、P29、P19、P18、P31、P23、P14、P1、P32、P16、P9、P26、P11、P21、P28、P27、P15、P8、P35、P37、P22</t>
+          <t>BL4、BL3</t>
         </is>
       </c>
     </row>
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>1.500-3.000</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>212.457</v>
+        <v>614.933</v>
       </c>
       <c r="E12" t="n">
-        <v>2337.028</v>
+        <v>6861.985</v>
       </c>
       <c r="F12" t="n">
-        <v>6309.976</v>
+        <v>18527.359</v>
       </c>
       <c r="G12" t="n">
-        <v>1.099</v>
+        <v>2.101</v>
       </c>
       <c r="H12" t="n">
-        <v>69.34</v>
+        <v>389.336</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P4、P2、P3、P5、P10、P13、P7、P17、P6</t>
+          <t>P38、P36、P33、P12、P30、P34、P29、P19、P18、P31、P23、P14、P1、P32、P16、P9、P26、P11、P21、P28、P27、P15、P8、P35、P37、P22</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -865,58 +865,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78.309</v>
+        <v>212.457</v>
       </c>
       <c r="E13" t="n">
-        <v>861.396</v>
+        <v>2337.028</v>
       </c>
       <c r="F13" t="n">
-        <v>2325.768</v>
+        <v>6309.976</v>
       </c>
       <c r="G13" t="n">
-        <v>1.143</v>
+        <v>1.099</v>
       </c>
       <c r="H13" t="n">
-        <v>26.591</v>
+        <v>69.34</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P25、P24、P20</t>
+          <t>P4、P2、P3、P5、P10、P13、P7、P17、P6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.500-3.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>83.342</v>
+        <v>78.309</v>
       </c>
       <c r="E14" t="n">
-        <v>916.763</v>
+        <v>861.396</v>
       </c>
       <c r="F14" t="n">
-        <v>2475.259</v>
+        <v>2325.768</v>
       </c>
       <c r="G14" t="n">
-        <v>1.545</v>
+        <v>1.143</v>
       </c>
       <c r="H14" t="n">
-        <v>38.243</v>
+        <v>26.591</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P30、P28</t>
+          <t>P25、P24、P20</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -935,23 +935,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.502</v>
+        <v>83.342</v>
       </c>
       <c r="E15" t="n">
-        <v>895.016</v>
+        <v>916.763</v>
       </c>
       <c r="F15" t="n">
-        <v>2416.545</v>
+        <v>2475.259</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>1.545</v>
       </c>
       <c r="H15" t="n">
-        <v>52.681</v>
+        <v>38.243</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P3、P2、P1</t>
+          <t>P30、P28</t>
         </is>
       </c>
     </row>
@@ -962,31 +962,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>1.500-3.000</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78.67100000000001</v>
+        <v>89.502</v>
       </c>
       <c r="E16" t="n">
-        <v>786.705</v>
+        <v>895.016</v>
       </c>
       <c r="F16" t="n">
-        <v>2124.105</v>
+        <v>2416.545</v>
       </c>
       <c r="G16" t="n">
-        <v>1.375</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="n">
-        <v>29.206</v>
+        <v>52.681</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>P6、P4</t>
+          <t>P3、P2、P1</t>
         </is>
       </c>
     </row>
@@ -997,66 +997,66 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>685.884</v>
+        <v>78.67100000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>7469.899</v>
+        <v>786.705</v>
       </c>
       <c r="F17" t="n">
-        <v>20168.728</v>
+        <v>2124.105</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>1.375</v>
       </c>
       <c r="H17" t="n">
-        <v>165.453</v>
+        <v>29.206</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
+          <t>P6、P4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>163.263</v>
+        <v>685.884</v>
       </c>
       <c r="E18" t="n">
-        <v>1897.084</v>
+        <v>7469.899</v>
       </c>
       <c r="F18" t="n">
-        <v>5122.126</v>
+        <v>20168.728</v>
       </c>
       <c r="G18" t="n">
-        <v>1.204</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>61.688</v>
+        <v>165.453</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>P2、P3、P5、P12、P1、P7</t>
+          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
         </is>
       </c>
     </row>
@@ -1067,31 +1067,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>114.812</v>
+        <v>163.263</v>
       </c>
       <c r="E19" t="n">
-        <v>1322.7</v>
+        <v>1897.084</v>
       </c>
       <c r="F19" t="n">
-        <v>3571.291</v>
+        <v>5122.126</v>
       </c>
       <c r="G19" t="n">
-        <v>0.729</v>
+        <v>1.204</v>
       </c>
       <c r="H19" t="n">
-        <v>26.039</v>
+        <v>61.688</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>P4、P9、P6、P8</t>
+          <t>P2、P3、P5、P12、P1、P7</t>
         </is>
       </c>
     </row>
@@ -1102,29 +1102,64 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>114.812</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1322.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3571.291</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H20" t="n">
+        <v>26.039</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>P4、P9、P6、P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>3</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>0.500-1.000</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>59.367</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>653.039</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>1763.206</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>0.68</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>11.99</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>P23、P14</t>
         </is>
@@ -1208,16 +1243,16 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1486.444</v>
+        <v>5329.066</v>
       </c>
       <c r="E3" t="n">
-        <v>4013.398</v>
+        <v>14388.478</v>
       </c>
       <c r="F3" t="n">
-        <v>54.193</v>
+        <v>154.691</v>
       </c>
     </row>
     <row r="4">
@@ -1363,7 +1398,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -1376,7 +1411,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 个矿孔原本落在矿界外（BL1、BL6）</t>
+          <t>2 个矿孔原本落在矿界外（BL1、BL6）；3 个矿孔原本落在矿界外（P9、P15、P17）</t>
         </is>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>282.905</v>
+        <v>290.37</v>
       </c>
       <c r="E2" t="n">
-        <v>3111.952</v>
+        <v>3194.073</v>
       </c>
       <c r="F2" t="n">
-        <v>8402.27</v>
+        <v>8623.998</v>
       </c>
       <c r="G2" t="n">
         <v>1.76</v>
       </c>
       <c r="H2" t="n">
-        <v>147.88</v>
+        <v>151.782</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76.89700000000001</v>
+        <v>73.786</v>
       </c>
       <c r="E4" t="n">
-        <v>768.967</v>
+        <v>737.86</v>
       </c>
       <c r="F4" t="n">
-        <v>2076.212</v>
+        <v>1992.223</v>
       </c>
       <c r="G4" t="n">
         <v>1.825</v>
       </c>
       <c r="H4" t="n">
-        <v>37.891</v>
+        <v>36.358</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>662.068</v>
+        <v>664.117</v>
       </c>
       <c r="E6" t="n">
-        <v>6492.225</v>
+        <v>6513.236</v>
       </c>
       <c r="F6" t="n">
-        <v>17529.007</v>
+        <v>17585.738</v>
       </c>
       <c r="G6" t="n">
         <v>1.263</v>
       </c>
       <c r="H6" t="n">
-        <v>221.351</v>
+        <v>222.067</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -830,23 +830,23 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>614.933</v>
+        <v>638.4880000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6861.985</v>
+        <v>7121.053</v>
       </c>
       <c r="F12" t="n">
-        <v>18527.359</v>
+        <v>19226.842</v>
       </c>
       <c r="G12" t="n">
-        <v>2.101</v>
+        <v>2.004</v>
       </c>
       <c r="H12" t="n">
-        <v>389.336</v>
+        <v>385.273</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P38、P36、P33、P12、P30、P34、P29、P19、P18、P31、P23、P14、P1、P32、P16、P9、P26、P11、P21、P28、P27、P15、P8、P35、P37、P22</t>
+          <t>P38、P36、P33、P12、P30、P34、P29、P19、P18、P31、P23、P14、P1、P32、P16、P9、P26、P11、P21、P28、P27、P15、P8、P35、P25、P37、P24、P22、P20</t>
         </is>
       </c>
     </row>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212.457</v>
+        <v>212.304</v>
       </c>
       <c r="E13" t="n">
-        <v>2337.028</v>
+        <v>2335.348</v>
       </c>
       <c r="F13" t="n">
-        <v>6309.976</v>
+        <v>6305.438</v>
       </c>
       <c r="G13" t="n">
         <v>1.099</v>
       </c>
       <c r="H13" t="n">
-        <v>69.34</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -888,35 +888,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>1.500-3.000</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78.309</v>
+        <v>83.342</v>
       </c>
       <c r="E14" t="n">
-        <v>861.396</v>
+        <v>916.763</v>
       </c>
       <c r="F14" t="n">
-        <v>2325.768</v>
+        <v>2475.259</v>
       </c>
       <c r="G14" t="n">
-        <v>1.143</v>
+        <v>1.545</v>
       </c>
       <c r="H14" t="n">
-        <v>26.591</v>
+        <v>38.243</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P25、P24、P20</t>
+          <t>P30、P28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -935,23 +935,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.342</v>
+        <v>89.502</v>
       </c>
       <c r="E15" t="n">
-        <v>916.763</v>
+        <v>895.016</v>
       </c>
       <c r="F15" t="n">
-        <v>2475.259</v>
+        <v>2416.545</v>
       </c>
       <c r="G15" t="n">
-        <v>1.545</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
-        <v>38.243</v>
+        <v>52.681</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P30、P28</t>
+          <t>P3、P2、P1</t>
         </is>
       </c>
     </row>
@@ -962,31 +962,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.500-3.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>89.502</v>
+        <v>78.16800000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>895.016</v>
+        <v>781.682</v>
       </c>
       <c r="F16" t="n">
-        <v>2416.545</v>
+        <v>2110.541</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>1.375</v>
       </c>
       <c r="H16" t="n">
-        <v>52.681</v>
+        <v>29.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>P3、P2、P1</t>
+          <t>P6、P4</t>
         </is>
       </c>
     </row>
@@ -997,66 +997,66 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78.67100000000001</v>
+        <v>672.726</v>
       </c>
       <c r="E17" t="n">
-        <v>786.705</v>
+        <v>7325.304</v>
       </c>
       <c r="F17" t="n">
-        <v>2124.105</v>
+        <v>19778.32</v>
       </c>
       <c r="G17" t="n">
-        <v>1.375</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>29.206</v>
+        <v>162.25</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>P6、P4</t>
+          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>685.884</v>
+        <v>163.263</v>
       </c>
       <c r="E18" t="n">
-        <v>7469.899</v>
+        <v>1897.084</v>
       </c>
       <c r="F18" t="n">
-        <v>20168.728</v>
+        <v>5122.126</v>
       </c>
       <c r="G18" t="n">
-        <v>0.82</v>
+        <v>1.204</v>
       </c>
       <c r="H18" t="n">
-        <v>165.453</v>
+        <v>61.688</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
+          <t>P2、P3、P5、P12、P1、P7</t>
         </is>
       </c>
     </row>
@@ -1067,31 +1067,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>163.263</v>
+        <v>114.812</v>
       </c>
       <c r="E19" t="n">
-        <v>1897.084</v>
+        <v>1322.7</v>
       </c>
       <c r="F19" t="n">
-        <v>5122.126</v>
+        <v>3571.291</v>
       </c>
       <c r="G19" t="n">
-        <v>1.204</v>
+        <v>0.729</v>
       </c>
       <c r="H19" t="n">
-        <v>61.688</v>
+        <v>26.039</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>P2、P3、P5、P12、P1、P7</t>
+          <t>P4、P9、P6、P8</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1110,56 +1110,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>114.812</v>
+        <v>59.367</v>
       </c>
       <c r="E20" t="n">
-        <v>1322.7</v>
+        <v>653.039</v>
       </c>
       <c r="F20" t="n">
-        <v>3571.291</v>
+        <v>1763.206</v>
       </c>
       <c r="G20" t="n">
-        <v>0.729</v>
+        <v>0.68</v>
       </c>
       <c r="H20" t="n">
-        <v>26.039</v>
+        <v>11.99</v>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>P4、P9、P6、P8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0.500-1.000</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>59.367</v>
-      </c>
-      <c r="E21" t="n">
-        <v>653.039</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1763.206</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H21" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>P23、P14</t>
         </is>
@@ -1224,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>12995.756</v>
+        <v>13067.782</v>
       </c>
       <c r="E2" t="n">
-        <v>35088.54</v>
+        <v>35283.01</v>
       </c>
       <c r="F2" t="n">
-        <v>531.426</v>
+        <v>534.5119999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1265,16 +1230,16 @@
         <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>10060.408</v>
+        <v>9456.4</v>
       </c>
       <c r="E4" t="n">
-        <v>27163.103</v>
+        <v>25532.28</v>
       </c>
       <c r="F4" t="n">
-        <v>485.266</v>
+        <v>454.562</v>
       </c>
     </row>
     <row r="5">
@@ -1290,13 +1255,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10068.384</v>
+        <v>9918.764999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>27184.637</v>
+        <v>26780.665</v>
       </c>
       <c r="F5" t="n">
-        <v>285.583</v>
+        <v>282.194</v>
       </c>
     </row>
     <row r="6">
@@ -1435,7 +1400,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>1 个矿孔原本落在矿界外（P19）</t>
         </is>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>638.4880000000001</v>
+        <v>629.71</v>
       </c>
       <c r="E12" t="n">
-        <v>7121.053</v>
+        <v>7024.218</v>
       </c>
       <c r="F12" t="n">
-        <v>19226.842</v>
+        <v>18965.39</v>
       </c>
       <c r="G12" t="n">
         <v>2.004</v>
       </c>
       <c r="H12" t="n">
-        <v>385.273</v>
+        <v>380.034</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212.304</v>
+        <v>213.858</v>
       </c>
       <c r="E13" t="n">
-        <v>2335.348</v>
+        <v>2352.433</v>
       </c>
       <c r="F13" t="n">
-        <v>6305.438</v>
+        <v>6351.57</v>
       </c>
       <c r="G13" t="n">
         <v>1.099</v>
       </c>
       <c r="H13" t="n">
-        <v>69.29000000000001</v>
+        <v>69.797</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1233,13 +1233,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9456.4</v>
+        <v>9376.652</v>
       </c>
       <c r="E4" t="n">
-        <v>25532.28</v>
+        <v>25316.959</v>
       </c>
       <c r="F4" t="n">
-        <v>454.562</v>
+        <v>449.83</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 个矿孔原本落在矿界外（P19）</t>
+          <t>OK</t>
         </is>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>664.117</v>
+        <v>691.064</v>
       </c>
       <c r="E6" t="n">
-        <v>6513.236</v>
+        <v>6728.817</v>
       </c>
       <c r="F6" t="n">
-        <v>17585.738</v>
+        <v>18167.806</v>
       </c>
       <c r="G6" t="n">
         <v>1.263</v>
       </c>
       <c r="H6" t="n">
-        <v>222.067</v>
+        <v>229.417</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>214.332</v>
+        <v>214.958</v>
       </c>
       <c r="E8" t="n">
-        <v>948.674</v>
+        <v>891.783</v>
       </c>
       <c r="F8" t="n">
-        <v>2561.42</v>
+        <v>2407.815</v>
       </c>
       <c r="G8" t="n">
         <v>1.727</v>
       </c>
       <c r="H8" t="n">
-        <v>44.227</v>
+        <v>41.575</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>308.969</v>
+        <v>338.579</v>
       </c>
       <c r="E9" t="n">
-        <v>1090.677</v>
+        <v>1196.277</v>
       </c>
       <c r="F9" t="n">
-        <v>2944.827</v>
+        <v>3229.947</v>
       </c>
       <c r="G9" t="n">
         <v>1.333</v>
       </c>
       <c r="H9" t="n">
-        <v>39.25</v>
+        <v>43.051</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>253.006</v>
+        <v>283.012</v>
       </c>
       <c r="E10" t="n">
-        <v>2728.153</v>
+        <v>3047.971</v>
       </c>
       <c r="F10" t="n">
-        <v>7366.014</v>
+        <v>8229.522999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0.824</v>
       </c>
       <c r="H10" t="n">
-        <v>60.675</v>
+        <v>67.788</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>283.238</v>
+        <v>339.922</v>
       </c>
       <c r="E11" t="n">
-        <v>561.562</v>
+        <v>661.559</v>
       </c>
       <c r="F11" t="n">
-        <v>1516.216</v>
+        <v>1786.21</v>
       </c>
       <c r="G11" t="n">
         <v>0.695</v>
       </c>
       <c r="H11" t="n">
-        <v>10.538</v>
+        <v>12.414</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>13067.782</v>
+        <v>13283.362</v>
       </c>
       <c r="E2" t="n">
-        <v>35283.01</v>
+        <v>35865.078</v>
       </c>
       <c r="F2" t="n">
-        <v>534.5119999999999</v>
+        <v>541.8630000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1211,13 +1211,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5329.066</v>
+        <v>5797.591</v>
       </c>
       <c r="E3" t="n">
-        <v>14388.478</v>
+        <v>15653.494</v>
       </c>
       <c r="F3" t="n">
-        <v>154.691</v>
+        <v>164.828</v>
       </c>
     </row>
     <row r="4">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,23 +900,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>83.342</v>
+        <v>167.67</v>
       </c>
       <c r="E14" t="n">
-        <v>916.763</v>
+        <v>1676.698</v>
       </c>
       <c r="F14" t="n">
-        <v>2475.259</v>
+        <v>4527.086</v>
       </c>
       <c r="G14" t="n">
-        <v>1.545</v>
+        <v>1.858</v>
       </c>
       <c r="H14" t="n">
-        <v>38.243</v>
+        <v>84.113</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P30、P28</t>
+          <t>P3、P2、P6、P1、P4</t>
         </is>
       </c>
     </row>
@@ -935,23 +935,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>89.502</v>
+        <v>83.342</v>
       </c>
       <c r="E15" t="n">
-        <v>895.016</v>
+        <v>916.763</v>
       </c>
       <c r="F15" t="n">
-        <v>2416.545</v>
+        <v>2475.259</v>
       </c>
       <c r="G15" t="n">
-        <v>2.18</v>
+        <v>1.545</v>
       </c>
       <c r="H15" t="n">
-        <v>52.681</v>
+        <v>38.243</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P3、P2、P1</t>
+          <t>P30、P28</t>
         </is>
       </c>
     </row>
@@ -966,62 +966,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78.16800000000001</v>
+        <v>672.726</v>
       </c>
       <c r="E16" t="n">
-        <v>781.682</v>
+        <v>7325.304</v>
       </c>
       <c r="F16" t="n">
-        <v>2110.541</v>
+        <v>19778.32</v>
       </c>
       <c r="G16" t="n">
-        <v>1.375</v>
+        <v>0.82</v>
       </c>
       <c r="H16" t="n">
-        <v>29.02</v>
+        <v>162.25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>P6、P4</t>
+          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>672.726</v>
+        <v>163.263</v>
       </c>
       <c r="E17" t="n">
-        <v>7325.304</v>
+        <v>1897.084</v>
       </c>
       <c r="F17" t="n">
-        <v>19778.32</v>
+        <v>5122.126</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>1.204</v>
       </c>
       <c r="H17" t="n">
-        <v>162.25</v>
+        <v>61.688</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
+          <t>P2、P3、P5、P12、P1、P7</t>
         </is>
       </c>
     </row>
@@ -1032,31 +1032,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>163.263</v>
+        <v>114.812</v>
       </c>
       <c r="E18" t="n">
-        <v>1897.084</v>
+        <v>1322.7</v>
       </c>
       <c r="F18" t="n">
-        <v>5122.126</v>
+        <v>3571.291</v>
       </c>
       <c r="G18" t="n">
-        <v>1.204</v>
+        <v>0.729</v>
       </c>
       <c r="H18" t="n">
-        <v>61.688</v>
+        <v>26.039</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>P2、P3、P5、P12、P1、P7</t>
+          <t>P4、P9、P6、P8</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1075,56 +1075,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>114.812</v>
+        <v>59.367</v>
       </c>
       <c r="E19" t="n">
-        <v>1322.7</v>
+        <v>653.039</v>
       </c>
       <c r="F19" t="n">
-        <v>3571.291</v>
+        <v>1763.206</v>
       </c>
       <c r="G19" t="n">
-        <v>0.729</v>
+        <v>0.68</v>
       </c>
       <c r="H19" t="n">
-        <v>26.039</v>
+        <v>11.99</v>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>P4、P9、P6、P8</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.500-1.000</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>59.367</v>
-      </c>
-      <c r="E20" t="n">
-        <v>653.039</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1763.206</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H20" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>P23、P14</t>
         </is>
@@ -1252,7 +1217,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>9918.764999999999</v>
@@ -1261,7 +1226,7 @@
         <v>26780.665</v>
       </c>
       <c r="F5" t="n">
-        <v>282.194</v>
+        <v>284.606</v>
       </c>
     </row>
     <row r="6">

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -690,19 +690,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>214.958</v>
+        <v>219.368</v>
       </c>
       <c r="E8" t="n">
-        <v>891.783</v>
+        <v>897.282</v>
       </c>
       <c r="F8" t="n">
-        <v>2407.815</v>
+        <v>2422.661</v>
       </c>
       <c r="G8" t="n">
         <v>1.727</v>
       </c>
       <c r="H8" t="n">
-        <v>41.575</v>
+        <v>41.831</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>338.579</v>
+        <v>365.364</v>
       </c>
       <c r="E9" t="n">
-        <v>1196.277</v>
+        <v>1292.135</v>
       </c>
       <c r="F9" t="n">
-        <v>3229.947</v>
+        <v>3488.765</v>
       </c>
       <c r="G9" t="n">
         <v>1.333</v>
       </c>
       <c r="H9" t="n">
-        <v>43.051</v>
+        <v>46.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>283.012</v>
+        <v>297.081</v>
       </c>
       <c r="E10" t="n">
-        <v>3047.971</v>
+        <v>3199.778</v>
       </c>
       <c r="F10" t="n">
-        <v>8229.522999999999</v>
+        <v>8639.401</v>
       </c>
       <c r="G10" t="n">
         <v>0.824</v>
       </c>
       <c r="H10" t="n">
-        <v>67.788</v>
+        <v>71.16500000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -795,19 +795,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>339.922</v>
+        <v>395.866</v>
       </c>
       <c r="E11" t="n">
-        <v>661.559</v>
+        <v>759.133</v>
       </c>
       <c r="F11" t="n">
-        <v>1786.21</v>
+        <v>2049.658</v>
       </c>
       <c r="G11" t="n">
         <v>0.695</v>
       </c>
       <c r="H11" t="n">
-        <v>12.414</v>
+        <v>14.245</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5797.591</v>
+        <v>6148.327</v>
       </c>
       <c r="E3" t="n">
-        <v>15653.494</v>
+        <v>16600.484</v>
       </c>
       <c r="F3" t="n">
-        <v>164.828</v>
+        <v>173.741</v>
       </c>
     </row>
     <row r="4">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 个矿孔原本落在矿界外（BL1、BL6）；3 个矿孔原本落在矿界外（P9、P15、P17）</t>
+          <t>矿界原本碎成 2 片；2 个矿孔原本落在矿界外（BL1、BL6）；3 个矿孔原本落在矿界外（P9、P15、P17）</t>
         </is>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,16 +623,16 @@
         <v>691.064</v>
       </c>
       <c r="E6" t="n">
-        <v>6728.817</v>
+        <v>6729.119</v>
       </c>
       <c r="F6" t="n">
-        <v>18167.806</v>
+        <v>18158.087</v>
       </c>
       <c r="G6" t="n">
-        <v>1.263</v>
+        <v>1.231</v>
       </c>
       <c r="H6" t="n">
-        <v>229.417</v>
+        <v>223.51</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -763,16 +763,16 @@
         <v>297.081</v>
       </c>
       <c r="E10" t="n">
-        <v>3199.778</v>
+        <v>3199.046</v>
       </c>
       <c r="F10" t="n">
-        <v>8639.401</v>
+        <v>8584.491</v>
       </c>
       <c r="G10" t="n">
-        <v>0.824</v>
+        <v>0.501</v>
       </c>
       <c r="H10" t="n">
-        <v>71.16500000000001</v>
+        <v>43.022</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -900,23 +900,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>167.67</v>
+        <v>83.342</v>
       </c>
       <c r="E14" t="n">
-        <v>1676.698</v>
+        <v>916.763</v>
       </c>
       <c r="F14" t="n">
-        <v>4527.086</v>
+        <v>2475.259</v>
       </c>
       <c r="G14" t="n">
-        <v>1.858</v>
+        <v>1.545</v>
       </c>
       <c r="H14" t="n">
-        <v>84.113</v>
+        <v>38.243</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P3、P2、P6、P1、P4</t>
+          <t>P30、P28</t>
         </is>
       </c>
     </row>
@@ -935,23 +935,23 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.342</v>
+        <v>89.502</v>
       </c>
       <c r="E15" t="n">
-        <v>916.763</v>
+        <v>895.016</v>
       </c>
       <c r="F15" t="n">
-        <v>2475.259</v>
+        <v>2416.545</v>
       </c>
       <c r="G15" t="n">
-        <v>1.545</v>
+        <v>2.18</v>
       </c>
       <c r="H15" t="n">
-        <v>38.243</v>
+        <v>52.681</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P30、P28</t>
+          <t>P3、P2、P1</t>
         </is>
       </c>
     </row>
@@ -966,62 +966,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>672.726</v>
+        <v>78.16800000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>7325.304</v>
+        <v>781.682</v>
       </c>
       <c r="F16" t="n">
-        <v>19778.32</v>
+        <v>2110.541</v>
       </c>
       <c r="G16" t="n">
-        <v>0.82</v>
+        <v>1.375</v>
       </c>
       <c r="H16" t="n">
-        <v>162.25</v>
+        <v>29.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
+          <t>P6、P4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.000-1.500</t>
+          <t>0.500-1.000</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>163.263</v>
+        <v>672.726</v>
       </c>
       <c r="E17" t="n">
-        <v>1897.084</v>
+        <v>7274.81</v>
       </c>
       <c r="F17" t="n">
-        <v>5122.126</v>
+        <v>19547.801</v>
       </c>
       <c r="G17" t="n">
-        <v>1.204</v>
+        <v>0.711</v>
       </c>
       <c r="H17" t="n">
-        <v>61.688</v>
+        <v>139.077</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>P2、P3、P5、P12、P1、P7</t>
+          <t>P8、P11、P5、P7、P20、P23、P26、P14、P12、P10、P29、P27、P9、P31、P21、P13</t>
         </is>
       </c>
     </row>
@@ -1032,31 +1032,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.500-1.000</t>
+          <t>1.000-1.500</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>114.812</v>
+        <v>163.263</v>
       </c>
       <c r="E18" t="n">
-        <v>1322.7</v>
+        <v>1897.084</v>
       </c>
       <c r="F18" t="n">
-        <v>3571.291</v>
+        <v>5122.126</v>
       </c>
       <c r="G18" t="n">
-        <v>0.729</v>
+        <v>1.204</v>
       </c>
       <c r="H18" t="n">
-        <v>26.039</v>
+        <v>61.688</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>P4、P9、P6、P8</t>
+          <t>P2、P3、P5、P12、P1、P7</t>
         </is>
       </c>
     </row>
@@ -1067,29 +1067,64 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.500-1.000</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>114.812</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1322.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3571.291</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H19" t="n">
+        <v>26.039</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P4、P9、P6、P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>3</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>0.500-1.000</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D20" t="n">
         <v>59.367</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>653.039</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>1763.206</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>0.68</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>11.99</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>P23、P14</t>
         </is>
@@ -1154,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>13283.362</v>
+        <v>13283.665</v>
       </c>
       <c r="E2" t="n">
-        <v>35865.078</v>
+        <v>35855.359</v>
       </c>
       <c r="F2" t="n">
-        <v>541.8630000000001</v>
+        <v>535.955</v>
       </c>
     </row>
     <row r="3">
@@ -1176,13 +1211,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>6148.327</v>
+        <v>6147.595</v>
       </c>
       <c r="E3" t="n">
-        <v>16600.484</v>
+        <v>16545.574</v>
       </c>
       <c r="F3" t="n">
-        <v>173.741</v>
+        <v>145.599</v>
       </c>
     </row>
     <row r="4">
@@ -1217,16 +1252,16 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>9918.764999999999</v>
+        <v>9868.271000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>26780.665</v>
+        <v>26550.146</v>
       </c>
       <c r="F5" t="n">
-        <v>284.606</v>
+        <v>259.02</v>
       </c>
     </row>
     <row r="6">

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -556,13 +556,13 @@
         <v>737.86</v>
       </c>
       <c r="F4" t="n">
-        <v>1992.223</v>
+        <v>1988.761</v>
       </c>
       <c r="G4" t="n">
         <v>1.825</v>
       </c>
       <c r="H4" t="n">
-        <v>36.358</v>
+        <v>36.295</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -760,19 +760,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>297.081</v>
+        <v>371.502</v>
       </c>
       <c r="E10" t="n">
-        <v>3199.046</v>
+        <v>3920.983</v>
       </c>
       <c r="F10" t="n">
-        <v>8584.491</v>
+        <v>10586.654</v>
       </c>
       <c r="G10" t="n">
-        <v>0.501</v>
+        <v>0.824</v>
       </c>
       <c r="H10" t="n">
-        <v>43.022</v>
+        <v>87.20399999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1008,16 +1008,16 @@
         <v>672.726</v>
       </c>
       <c r="E17" t="n">
-        <v>7274.81</v>
+        <v>7265.822</v>
       </c>
       <c r="F17" t="n">
-        <v>19547.801</v>
+        <v>19520.439</v>
       </c>
       <c r="G17" t="n">
         <v>0.711</v>
       </c>
       <c r="H17" t="n">
-        <v>139.077</v>
+        <v>138.882</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         <v>1897.084</v>
       </c>
       <c r="F18" t="n">
-        <v>5122.126</v>
+        <v>5120.961</v>
       </c>
       <c r="G18" t="n">
         <v>1.204</v>
       </c>
       <c r="H18" t="n">
-        <v>61.688</v>
+        <v>61.674</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1078,16 +1078,16 @@
         <v>114.812</v>
       </c>
       <c r="E19" t="n">
-        <v>1322.7</v>
+        <v>1322.419</v>
       </c>
       <c r="F19" t="n">
-        <v>3571.291</v>
+        <v>3569.482</v>
       </c>
       <c r="G19" t="n">
         <v>0.729</v>
       </c>
       <c r="H19" t="n">
-        <v>26.039</v>
+        <v>26.026</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1113,16 +1113,16 @@
         <v>59.367</v>
       </c>
       <c r="E20" t="n">
-        <v>653.039</v>
+        <v>654.462</v>
       </c>
       <c r="F20" t="n">
-        <v>1763.206</v>
+        <v>1764.876</v>
       </c>
       <c r="G20" t="n">
         <v>0.68</v>
       </c>
       <c r="H20" t="n">
-        <v>11.99</v>
+        <v>12.001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         <v>13283.665</v>
       </c>
       <c r="E2" t="n">
-        <v>35855.359</v>
+        <v>35851.897</v>
       </c>
       <c r="F2" t="n">
-        <v>535.955</v>
+        <v>535.8920000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1211,13 +1211,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>6147.595</v>
+        <v>6869.532</v>
       </c>
       <c r="E3" t="n">
-        <v>16545.574</v>
+        <v>18547.737</v>
       </c>
       <c r="F3" t="n">
-        <v>145.599</v>
+        <v>189.781</v>
       </c>
     </row>
     <row r="4">
@@ -1255,13 +1255,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>9868.271000000001</v>
+        <v>9859.282999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>26550.146</v>
+        <v>26522.784</v>
       </c>
       <c r="F5" t="n">
-        <v>259.02</v>
+        <v>258.826</v>
       </c>
     </row>
     <row r="6">
@@ -1277,13 +1277,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3872.823</v>
+        <v>3873.965</v>
       </c>
       <c r="E6" t="n">
-        <v>10456.623</v>
+        <v>10455.32</v>
       </c>
       <c r="F6" t="n">
-        <v>99.717</v>
+        <v>99.702</v>
       </c>
     </row>
   </sheetData>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>矿界原本碎成 2 片；2 个矿孔原本落在矿界外（BL1、BL6）；3 个矿孔原本落在矿界外（P9、P15、P17）</t>
+          <t>矿界原本碎成 2 片；2 个矿孔原本落在矿界外（BL1、BL6）</t>
         </is>
       </c>
     </row>

--- a/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
+++ b/北部山头3940平台2026/7、单日数据/_批量汇总/批量汇总.xlsx
@@ -10,6 +10,7 @@
     <sheet name="明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="按日合计" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="参数" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="并图状态" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1455,4 +1456,130 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>已并入块数</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>总块数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>各块与综合图的最大重叠率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1号95% 2号91% 3号73% 4号89% 5号47% 6号87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0922</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1号0% 2号0% 3号4% 4号0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1号92% 2号94%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1号74% 2号69% 3号56% 4号93%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1号0% 2号0% 3号0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>